--- a/artfynd/A 22038-2026 artfynd.xlsx
+++ b/artfynd/A 22038-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134148467</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134148305</v>
       </c>
       <c r="B3" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22038-2026 artfynd.xlsx
+++ b/artfynd/A 22038-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134304095</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ekelundstorpet, Ekelundstorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468250</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6253943</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22038-2026 artfynd.xlsx
+++ b/artfynd/A 22038-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134148305</v>
+        <v>134304095</v>
       </c>
       <c r="B3" t="n">
-        <v>58134</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,29 +814,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ekelundstorpet, Ekelundstorpet, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468282</v>
+        <v>468250</v>
       </c>
       <c r="R3" t="n">
-        <v>6253953</v>
+        <v>6253943</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134304095</v>
+        <v>134148305</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>58134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,20 +921,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ekelundstorpet, Ekelundstorpet, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468250</v>
+        <v>468282</v>
       </c>
       <c r="R4" t="n">
-        <v>6253943</v>
+        <v>6253953</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,22 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,6 +1006,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134069968</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ekelundstorpet, Ekelundstorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>468161</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6253808</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
